--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95887</v>
+        <v>95892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95892</v>
+        <v>95895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95905</v>
+        <v>95912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95912</v>
+        <v>95914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95914</v>
+        <v>95940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95940</v>
+        <v>95941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95942</v>
+        <v>95946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128916086</v>
       </c>
       <c r="B2" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128916086</v>
+        <v>123248646</v>
       </c>
       <c r="B2" t="n">
-        <v>95952</v>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lundängen, Lundängen, Ög</t>
+          <t>Vinstorp, V, Sturefors (7), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541832</v>
+        <v>541901</v>
       </c>
       <c r="R2" t="n">
-        <v>6467891</v>
+        <v>6467991</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Första observationerna av bombmurkla i den här skogen! Gammal, mossig granskog där enstaka granar har avverkats precis i närheten. Längre bort finns större avverkade områden. Se biotopbilder. Få angripna/döda granar. Totalt sågs 13 stora bombmurklor i området, har noterats som flera delloklaler.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,21 +766,133 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Karin Nyström, Bengt Nyström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128916086</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lundängen, Lundängen, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>541832</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6467891</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Johan Holmgren</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Johan Holmgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48298-2025 artfynd.xlsx
+++ b/artfynd/A 48298-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123248646</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,8 +903,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128916086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>